--- a/OldTiwtch.xlsx
+++ b/OldTiwtch.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,46 +439,39 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Date/time</t>
+          <t>Date &amp; time CDT</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
           <t>Twitch's Users In Chat</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>my Users in Chat</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aikasanvr</t>
+          <t>Kareeda</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dead by Daylight</t>
+          <t>VRChat</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4375</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+        <v>10918</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2021-10-03 00:24:02</t>
+          <t>2021-10-09 21:24:13</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>152</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
